--- a/lista_eventos_vl550v5.xlsx
+++ b/lista_eventos_vl550v5.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="24" documentId="8_{895CD3FE-E58D-4200-A1D0-1D06EA3EF3CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CEE6F59E-5426-4933-8C5D-D7440F48B0B0}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-48" windowWidth="23256" windowHeight="12456" xr2:uid="{3CD72D0F-0109-4709-BAE3-D4DAF02C6335}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{3CD72D0F-0109-4709-BAE3-D4DAF02C6335}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
